--- a/fixtures/saxo-nl/Transactions_10000000_2022-01-01_2022-12-31.xlsx
+++ b/fixtures/saxo-nl/Transactions_10000000_2022-01-01_2022-12-31.xlsx
@@ -8,13 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="Transacties" sheetId="1" r:id="rId1"/>
+    <sheet name="_Transacties" sheetId="2" r:id="rId2"/>
+    <sheet name="Bookings" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="276">
   <si>
     <t>Klant-id</t>
   </si>
@@ -172,297 +174,685 @@
     <t>40100/9000001EUR</t>
   </si>
   <si>
+    <t>40000000923</t>
+  </si>
+  <si>
+    <t>Geldoverboeking</t>
+  </si>
+  <si>
+    <t>Service fee</t>
+  </si>
+  <si>
+    <t>Saxo Service Fee Green - November 2022</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>5000069</t>
+  </si>
+  <si>
+    <t>40000000884</t>
+  </si>
+  <si>
+    <t>Saxo Service Fee Green - October 2022</t>
+  </si>
+  <si>
+    <t>5000063</t>
+  </si>
+  <si>
+    <t>40000000845</t>
+  </si>
+  <si>
+    <t>Saxo Service Fee Green - September 2022</t>
+  </si>
+  <si>
+    <t>5000042</t>
+  </si>
+  <si>
+    <t>5000057</t>
+  </si>
+  <si>
+    <t>40000000780</t>
+  </si>
+  <si>
+    <t>40000000767</t>
+  </si>
+  <si>
+    <t>Rente</t>
+  </si>
+  <si>
+    <t>Client Interest - Aug 2022</t>
+  </si>
+  <si>
+    <t>40000000754</t>
+  </si>
+  <si>
+    <t>5000048</t>
+  </si>
+  <si>
+    <t>2500000323</t>
+  </si>
+  <si>
+    <t>5000072</t>
+  </si>
+  <si>
+    <t>Stock split</t>
+  </si>
+  <si>
+    <t>Fixture Instrument 12</t>
+  </si>
+  <si>
+    <t>FXT13:xnas</t>
+  </si>
+  <si>
+    <t>XF0000000160</t>
+  </si>
+  <si>
+    <t>NASDAQ</t>
+  </si>
+  <si>
+    <t>5000066</t>
+  </si>
+  <si>
+    <t>Herbeleggingsdividend</t>
+  </si>
+  <si>
+    <t>Fixture Instrument 02</t>
+  </si>
+  <si>
+    <t>FXT01:xams</t>
+  </si>
+  <si>
+    <t>XF0000000111</t>
+  </si>
+  <si>
+    <t>Euronext Amsterdam</t>
+  </si>
+  <si>
+    <t>5000060</t>
+  </si>
+  <si>
+    <t>Fixture Instrument 03</t>
+  </si>
+  <si>
+    <t>FXT03:xams</t>
+  </si>
+  <si>
+    <t>XF0000000087</t>
+  </si>
+  <si>
+    <t>40000000650</t>
+  </si>
+  <si>
+    <t>Client Interest - Jul 2022</t>
+  </si>
+  <si>
+    <t>40000000637</t>
+  </si>
+  <si>
+    <t>40000000663</t>
+  </si>
+  <si>
+    <t>5000045</t>
+  </si>
+  <si>
+    <t>40000000598</t>
+  </si>
+  <si>
+    <t>40000000585</t>
+  </si>
+  <si>
+    <t>Client Interest - Jun 2022</t>
+  </si>
+  <si>
+    <t>40000000572</t>
+  </si>
+  <si>
+    <t>5000030</t>
+  </si>
+  <si>
+    <t>5000036</t>
+  </si>
+  <si>
+    <t>5000039</t>
+  </si>
+  <si>
+    <t>Keuzedividend</t>
+  </si>
+  <si>
+    <t>Fixture Instrument 11</t>
+  </si>
+  <si>
+    <t>FXT08:xams</t>
+  </si>
+  <si>
+    <t>XF0000000095</t>
+  </si>
+  <si>
+    <t>2500000306</t>
+  </si>
+  <si>
+    <t>40000000494</t>
+  </si>
+  <si>
+    <t>5000033</t>
+  </si>
+  <si>
+    <t>5000054</t>
+  </si>
+  <si>
+    <t>Fixture Instrument 10</t>
+  </si>
+  <si>
+    <t>FXT07</t>
+  </si>
+  <si>
+    <t>XF0000000129</t>
+  </si>
+  <si>
+    <t>MutualFund</t>
+  </si>
+  <si>
+    <t>Euronext Amsterdam Funds</t>
+  </si>
+  <si>
+    <t>5000051</t>
+  </si>
+  <si>
+    <t>5000024</t>
+  </si>
+  <si>
+    <t>40000000377</t>
+  </si>
+  <si>
+    <t>5000027</t>
+  </si>
+  <si>
+    <t>5000006</t>
+  </si>
+  <si>
+    <t>7000000098</t>
+  </si>
+  <si>
+    <t>2500000289</t>
+  </si>
+  <si>
+    <t>Transactie</t>
+  </si>
+  <si>
+    <t>Koop 40 @ 5.68 USD</t>
+  </si>
+  <si>
+    <t>Fixture Instrument 01</t>
+  </si>
+  <si>
+    <t>FXT14:xnas</t>
+  </si>
+  <si>
+    <t>XF0000000137</t>
+  </si>
+  <si>
+    <t>NASDAQ (Small cap)</t>
+  </si>
+  <si>
+    <t>7000000091</t>
+  </si>
+  <si>
+    <t>2500000272</t>
+  </si>
+  <si>
+    <t>Verkoop -60 @ 32.98 EUR</t>
+  </si>
+  <si>
+    <t>Fixture Instrument 16</t>
+  </si>
+  <si>
+    <t>FXT00:xams</t>
+  </si>
+  <si>
+    <t>XF0000000046</t>
+  </si>
+  <si>
+    <t>Etf</t>
+  </si>
+  <si>
+    <t>40000000260</t>
+  </si>
+  <si>
+    <t>5000015</t>
+  </si>
+  <si>
+    <t>5000021</t>
+  </si>
+  <si>
+    <t>40000000195</t>
+  </si>
+  <si>
+    <t>5000012</t>
+  </si>
+  <si>
+    <t>40000000156</t>
+  </si>
+  <si>
+    <t>5000009</t>
+  </si>
+  <si>
+    <t>5000018</t>
+  </si>
+  <si>
+    <t>Fixture Instrument 04</t>
+  </si>
+  <si>
+    <t>FXT06</t>
+  </si>
+  <si>
+    <t>XF0000000103</t>
+  </si>
+  <si>
+    <t>Bond</t>
+  </si>
+  <si>
+    <t>Euronext Amsterdam Bonds</t>
+  </si>
+  <si>
+    <t>40000000104</t>
+  </si>
+  <si>
+    <t>Order-ID</t>
+  </si>
+  <si>
+    <t>Aangepaste transactiedatum</t>
+  </si>
+  <si>
+    <t>Uitvoeringsdatum transactie</t>
+  </si>
+  <si>
+    <t>Trade Event Type</t>
+  </si>
+  <si>
+    <t>Trade Type</t>
+  </si>
+  <si>
+    <t>Openen/sluiten</t>
+  </si>
+  <si>
+    <t>Traded Quantity</t>
+  </si>
+  <si>
+    <t>Prijs</t>
+  </si>
+  <si>
+    <t>Verhandelde waarde</t>
+  </si>
+  <si>
+    <t>Spreadkosten</t>
+  </si>
+  <si>
+    <t>7000000112</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Verkocht</t>
+  </si>
+  <si>
+    <t>NotAvailable</t>
+  </si>
+  <si>
+    <t>Te sluiten</t>
+  </si>
+  <si>
+    <t>7000000119</t>
+  </si>
+  <si>
+    <t>Gekocht</t>
+  </si>
+  <si>
+    <t>Te openen</t>
+  </si>
+  <si>
+    <t>7000000105</t>
+  </si>
+  <si>
+    <t>6000000019</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>6000000000</t>
+  </si>
+  <si>
+    <t>Limit</t>
+  </si>
+  <si>
+    <t>Amount Type</t>
+  </si>
+  <si>
+    <t>Amount Type Id</t>
+  </si>
+  <si>
+    <t>Boekingsdatum</t>
+  </si>
+  <si>
+    <t>Ex-datum</t>
+  </si>
+  <si>
+    <t>Boekdatum</t>
+  </si>
+  <si>
+    <t>In aanmerking komend aantal</t>
+  </si>
+  <si>
+    <t>Dividend per aandeel</t>
+  </si>
+  <si>
+    <t>Tax Percentage</t>
+  </si>
+  <si>
+    <t>40000000962</t>
+  </si>
+  <si>
+    <t>Corporate Actions - Cashdividenden</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>14-dec-2022</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>0.09 CAD</t>
+  </si>
+  <si>
+    <t>40000000975</t>
+  </si>
+  <si>
+    <t>Corporate actions - Voorheffing</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>40000000936</t>
+  </si>
+  <si>
+    <t>16-nov-2022</t>
+  </si>
+  <si>
+    <t>11-okt-2022</t>
+  </si>
+  <si>
+    <t>0.70 USD</t>
+  </si>
+  <si>
+    <t>40000000949</t>
+  </si>
+  <si>
+    <t>477</t>
+  </si>
+  <si>
+    <t>40000000897</t>
+  </si>
+  <si>
+    <t>14-nov-2022</t>
+  </si>
+  <si>
+    <t>40000000910</t>
+  </si>
+  <si>
+    <t>40000000858</t>
+  </si>
+  <si>
+    <t>13-okt-2022</t>
+  </si>
+  <si>
+    <t>40000000871</t>
+  </si>
+  <si>
+    <t>40000000819</t>
+  </si>
+  <si>
+    <t>14-sep-2022</t>
+  </si>
+  <si>
+    <t>40000000832</t>
+  </si>
+  <si>
+    <t>40000000806</t>
+  </si>
+  <si>
+    <t>17-aug-2022</t>
+  </si>
+  <si>
+    <t>16-jun-2022</t>
+  </si>
+  <si>
+    <t>40000000793</t>
+  </si>
+  <si>
+    <t>0.57 USD</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>40000000728</t>
+  </si>
+  <si>
+    <t>12-aug-2022</t>
+  </si>
+  <si>
+    <t>40000000741</t>
+  </si>
+  <si>
+    <t>40000000715</t>
+  </si>
+  <si>
+    <t>Corporate actions - Fracties</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>08-aug-2022</t>
+  </si>
+  <si>
+    <t>40000000702</t>
+  </si>
+  <si>
+    <t>40000000676</t>
+  </si>
+  <si>
+    <t>29-jul-2022</t>
+  </si>
+  <si>
+    <t>27-jul-2022</t>
+  </si>
+  <si>
+    <t>40000000689</t>
+  </si>
+  <si>
+    <t>40000000611</t>
+  </si>
+  <si>
+    <t>14-jul-2022</t>
+  </si>
+  <si>
+    <t>40000000624</t>
+  </si>
+  <si>
+    <t>40000000546</t>
+  </si>
+  <si>
+    <t>14-jun-2022</t>
+  </si>
+  <si>
+    <t>40000000559</t>
+  </si>
+  <si>
+    <t>40000000507</t>
+  </si>
+  <si>
+    <t>18-mei-2022</t>
+  </si>
+  <si>
+    <t>16-mrt-2022</t>
+  </si>
+  <si>
+    <t>40000000520</t>
+  </si>
+  <si>
+    <t>40000000533</t>
+  </si>
+  <si>
+    <t>12-mei-2022</t>
+  </si>
+  <si>
+    <t>40000000468</t>
+  </si>
+  <si>
+    <t>40000000481</t>
+  </si>
+  <si>
+    <t>40000000455</t>
+  </si>
+  <si>
+    <t>19-mei-2022</t>
+  </si>
+  <si>
+    <t>1.43 EUR</t>
+  </si>
+  <si>
+    <t>40000000442</t>
+  </si>
+  <si>
+    <t>40000000416</t>
+  </si>
+  <si>
+    <t>10-mei-2022</t>
+  </si>
+  <si>
+    <t>40000000429</t>
+  </si>
+  <si>
+    <t>40000000403</t>
+  </si>
+  <si>
+    <t>27-apr-2022</t>
+  </si>
+  <si>
+    <t>21-dec-2021</t>
+  </si>
+  <si>
+    <t>40000000390</t>
+  </si>
+  <si>
+    <t>40000000351</t>
+  </si>
+  <si>
+    <t>13-apr-2022</t>
+  </si>
+  <si>
+    <t>40000000364</t>
+  </si>
+  <si>
+    <t>40000000325</t>
+  </si>
+  <si>
+    <t>19-apr-2022</t>
+  </si>
+  <si>
+    <t>26-okt-2021</t>
+  </si>
+  <si>
+    <t>40000000338</t>
+  </si>
+  <si>
+    <t>40000000299</t>
+  </si>
+  <si>
+    <t>Aandeelbedrag</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>40000000286</t>
+  </si>
+  <si>
+    <t>Commissie</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>40000000312</t>
+  </si>
+  <si>
     <t>40000000273</t>
   </si>
   <si>
-    <t>Geldoverboeking</t>
-  </si>
-  <si>
-    <t>Service fee</t>
-  </si>
-  <si>
-    <t>Saxo Service Fee Green - November 2022</t>
-  </si>
-  <si>
-    <t>Cash</t>
-  </si>
-  <si>
-    <t>5000069</t>
-  </si>
-  <si>
-    <t>40000000260</t>
-  </si>
-  <si>
-    <t>Saxo Service Fee Green - October 2022</t>
-  </si>
-  <si>
-    <t>5000063</t>
+    <t>40000000234</t>
+  </si>
+  <si>
+    <t>14-mrt-2022</t>
   </si>
   <si>
     <t>40000000247</t>
   </si>
   <si>
-    <t>Saxo Service Fee Green - September 2022</t>
-  </si>
-  <si>
-    <t>5000042</t>
-  </si>
-  <si>
-    <t>5000057</t>
-  </si>
-  <si>
-    <t>40000000234</t>
-  </si>
-  <si>
     <t>40000000221</t>
   </si>
   <si>
-    <t>Rente</t>
-  </si>
-  <si>
-    <t>Client Interest - Aug 2022</t>
+    <t>16-feb-2022</t>
   </si>
   <si>
     <t>40000000208</t>
   </si>
   <si>
-    <t>5000048</t>
-  </si>
-  <si>
-    <t>2500000323</t>
-  </si>
-  <si>
-    <t>5000072</t>
-  </si>
-  <si>
-    <t>Stock split</t>
-  </si>
-  <si>
-    <t>Fixture Instrument 12</t>
-  </si>
-  <si>
-    <t>FXT13:xnas</t>
-  </si>
-  <si>
-    <t>XF0000000160</t>
-  </si>
-  <si>
-    <t>NASDAQ</t>
-  </si>
-  <si>
-    <t>5000066</t>
-  </si>
-  <si>
-    <t>Herbeleggingsdividend</t>
-  </si>
-  <si>
-    <t>Fixture Instrument 02</t>
-  </si>
-  <si>
-    <t>FXT01:xams</t>
-  </si>
-  <si>
-    <t>XF0000000111</t>
-  </si>
-  <si>
-    <t>Euronext Amsterdam</t>
-  </si>
-  <si>
-    <t>5000060</t>
-  </si>
-  <si>
-    <t>Fixture Instrument 03</t>
-  </si>
-  <si>
-    <t>FXT03:xams</t>
-  </si>
-  <si>
-    <t>XF0000000087</t>
-  </si>
-  <si>
     <t>40000000182</t>
   </si>
   <si>
-    <t>Client Interest - Jul 2022</t>
+    <t>14-feb-2022</t>
   </si>
   <si>
     <t>40000000169</t>
   </si>
   <si>
-    <t>40000000195</t>
-  </si>
-  <si>
-    <t>5000045</t>
-  </si>
-  <si>
-    <t>40000000156</t>
+    <t>40000000130</t>
+  </si>
+  <si>
+    <t>13-jan-2022</t>
   </si>
   <si>
     <t>40000000143</t>
   </si>
   <si>
-    <t>Client Interest - Jun 2022</t>
-  </si>
-  <si>
-    <t>40000000130</t>
-  </si>
-  <si>
-    <t>5000030</t>
-  </si>
-  <si>
-    <t>5000036</t>
-  </si>
-  <si>
-    <t>5000039</t>
-  </si>
-  <si>
-    <t>Keuzedividend</t>
-  </si>
-  <si>
-    <t>Fixture Instrument 11</t>
-  </si>
-  <si>
-    <t>FXT08:xams</t>
-  </si>
-  <si>
-    <t>XF0000000095</t>
-  </si>
-  <si>
-    <t>2500000306</t>
-  </si>
-  <si>
     <t>40000000117</t>
   </si>
   <si>
-    <t>5000033</t>
-  </si>
-  <si>
-    <t>5000054</t>
-  </si>
-  <si>
-    <t>Fixture Instrument 10</t>
-  </si>
-  <si>
-    <t>FXT07</t>
-  </si>
-  <si>
-    <t>XF0000000129</t>
-  </si>
-  <si>
-    <t>MutualFund</t>
-  </si>
-  <si>
-    <t>Euronext Amsterdam Funds</t>
-  </si>
-  <si>
-    <t>5000051</t>
-  </si>
-  <si>
-    <t>5000024</t>
-  </si>
-  <si>
-    <t>40000000104</t>
-  </si>
-  <si>
-    <t>5000027</t>
-  </si>
-  <si>
-    <t>5000006</t>
-  </si>
-  <si>
-    <t>7000000098</t>
-  </si>
-  <si>
-    <t>2500000289</t>
-  </si>
-  <si>
-    <t>Transactie</t>
-  </si>
-  <si>
-    <t>Koop 40 @ 5.68 USD</t>
-  </si>
-  <si>
-    <t>Fixture Instrument 01</t>
-  </si>
-  <si>
-    <t>FXT14:xnas</t>
-  </si>
-  <si>
-    <t>XF0000000137</t>
-  </si>
-  <si>
-    <t>NASDAQ (Small cap)</t>
-  </si>
-  <si>
-    <t>7000000091</t>
-  </si>
-  <si>
-    <t>2500000272</t>
-  </si>
-  <si>
-    <t>Verkoop -60 @ 32.98 EUR</t>
-  </si>
-  <si>
-    <t>Fixture Instrument 16</t>
-  </si>
-  <si>
-    <t>FXT00:xams</t>
-  </si>
-  <si>
-    <t>XF0000000046</t>
-  </si>
-  <si>
-    <t>Etf</t>
-  </si>
-  <si>
-    <t>40000000091</t>
-  </si>
-  <si>
-    <t>5000015</t>
-  </si>
-  <si>
-    <t>5000021</t>
-  </si>
-  <si>
-    <t>40000000078</t>
-  </si>
-  <si>
-    <t>5000012</t>
-  </si>
-  <si>
-    <t>40000000065</t>
-  </si>
-  <si>
-    <t>5000009</t>
-  </si>
-  <si>
-    <t>5000018</t>
-  </si>
-  <si>
-    <t>Fixture Instrument 04</t>
-  </si>
-  <si>
-    <t>FXT06</t>
-  </si>
-  <si>
-    <t>XF0000000103</t>
-  </si>
-  <si>
-    <t>Bond</t>
-  </si>
-  <si>
-    <t>Euronext Amsterdam Bonds</t>
-  </si>
-  <si>
-    <t>40000000052</t>
+    <t>Rente obligatiecoupon</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>31-dec-2021</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy hh:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -493,9 +883,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3809,4 +4200,4254 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:X6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:24">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K1" t="s">
+        <v>151</v>
+      </c>
+      <c r="L1" t="s">
+        <v>152</v>
+      </c>
+      <c r="M1" t="s">
+        <v>153</v>
+      </c>
+      <c r="N1" t="s">
+        <v>154</v>
+      </c>
+      <c r="O1" t="s">
+        <v>155</v>
+      </c>
+      <c r="P1" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1" t="s">
+        <v>25</v>
+      </c>
+      <c r="V1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
+      <c r="A2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H2" s="1">
+        <v>44798</v>
+      </c>
+      <c r="I2" s="2">
+        <v>44798.9262152778</v>
+      </c>
+      <c r="J2" t="s">
+        <v>159</v>
+      </c>
+      <c r="K2" t="s">
+        <v>160</v>
+      </c>
+      <c r="L2" t="s">
+        <v>161</v>
+      </c>
+      <c r="M2">
+        <v>-15</v>
+      </c>
+      <c r="N2">
+        <v>151.57</v>
+      </c>
+      <c r="O2">
+        <v>2273.56</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" t="s">
+        <v>74</v>
+      </c>
+      <c r="T2" t="s">
+        <v>75</v>
+      </c>
+      <c r="U2" t="s">
+        <v>76</v>
+      </c>
+      <c r="V2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H3" s="1">
+        <v>44798</v>
+      </c>
+      <c r="I3" s="2">
+        <v>44798.9262152778</v>
+      </c>
+      <c r="J3" t="s">
+        <v>163</v>
+      </c>
+      <c r="K3" t="s">
+        <v>160</v>
+      </c>
+      <c r="L3" t="s">
+        <v>164</v>
+      </c>
+      <c r="M3">
+        <v>45</v>
+      </c>
+      <c r="N3">
+        <v>50.68</v>
+      </c>
+      <c r="O3">
+        <v>-2280.77</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" t="s">
+        <v>74</v>
+      </c>
+      <c r="T3" t="s">
+        <v>75</v>
+      </c>
+      <c r="U3" t="s">
+        <v>76</v>
+      </c>
+      <c r="V3" t="s">
+        <v>46</v>
+      </c>
+      <c r="W3" t="s">
+        <v>41</v>
+      </c>
+      <c r="X3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
+      <c r="A4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G4" t="s">
+        <v>158</v>
+      </c>
+      <c r="H4" s="1">
+        <v>44720</v>
+      </c>
+      <c r="I4" s="2">
+        <v>44720.4649189815</v>
+      </c>
+      <c r="J4" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" t="s">
+        <v>160</v>
+      </c>
+      <c r="L4" t="s">
+        <v>164</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>21.8</v>
+      </c>
+      <c r="O4">
+        <v>-21.8</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S4" t="s">
+        <v>101</v>
+      </c>
+      <c r="T4" t="s">
+        <v>102</v>
+      </c>
+      <c r="U4" t="s">
+        <v>103</v>
+      </c>
+      <c r="V4" t="s">
+        <v>36</v>
+      </c>
+      <c r="W4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5">
+        <v>3000000055</v>
+      </c>
+      <c r="F5" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" t="s">
+        <v>166</v>
+      </c>
+      <c r="H5" s="1">
+        <v>44655</v>
+      </c>
+      <c r="I5" s="2">
+        <v>44655.5626157407</v>
+      </c>
+      <c r="J5" t="s">
+        <v>163</v>
+      </c>
+      <c r="K5" t="s">
+        <v>167</v>
+      </c>
+      <c r="L5" t="s">
+        <v>164</v>
+      </c>
+      <c r="M5">
+        <v>40</v>
+      </c>
+      <c r="N5">
+        <v>5.68</v>
+      </c>
+      <c r="O5">
+        <v>-227</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>43</v>
+      </c>
+      <c r="S5" t="s">
+        <v>122</v>
+      </c>
+      <c r="T5" t="s">
+        <v>123</v>
+      </c>
+      <c r="U5" t="s">
+        <v>124</v>
+      </c>
+      <c r="V5" t="s">
+        <v>46</v>
+      </c>
+      <c r="W5" t="s">
+        <v>41</v>
+      </c>
+      <c r="X5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6">
+        <v>3000000044</v>
+      </c>
+      <c r="F6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G6" t="s">
+        <v>168</v>
+      </c>
+      <c r="H6" s="1">
+        <v>44655</v>
+      </c>
+      <c r="I6" s="2">
+        <v>44655.2951388889</v>
+      </c>
+      <c r="J6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K6" t="s">
+        <v>169</v>
+      </c>
+      <c r="L6" t="s">
+        <v>161</v>
+      </c>
+      <c r="M6">
+        <v>-60</v>
+      </c>
+      <c r="N6">
+        <v>32.98</v>
+      </c>
+      <c r="O6">
+        <v>1979.06</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>43</v>
+      </c>
+      <c r="S6" t="s">
+        <v>129</v>
+      </c>
+      <c r="T6" t="s">
+        <v>130</v>
+      </c>
+      <c r="U6" t="s">
+        <v>131</v>
+      </c>
+      <c r="V6" t="s">
+        <v>36</v>
+      </c>
+      <c r="W6" t="s">
+        <v>132</v>
+      </c>
+      <c r="X6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:U69"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:21">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" t="s">
+        <v>172</v>
+      </c>
+      <c r="M1" t="s">
+        <v>173</v>
+      </c>
+      <c r="N1" t="s">
+        <v>174</v>
+      </c>
+      <c r="O1" t="s">
+        <v>175</v>
+      </c>
+      <c r="P1" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>177</v>
+      </c>
+      <c r="R1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1" t="s">
+        <v>25</v>
+      </c>
+      <c r="U1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>3000000363</v>
+      </c>
+      <c r="D2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I2">
+        <v>17.55</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0.699873</v>
+      </c>
+      <c r="L2" s="1">
+        <v>44925</v>
+      </c>
+      <c r="M2" t="s">
+        <v>181</v>
+      </c>
+      <c r="N2" t="s">
+        <v>182</v>
+      </c>
+      <c r="O2">
+        <v>300</v>
+      </c>
+      <c r="P2" t="s">
+        <v>183</v>
+      </c>
+      <c r="R2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3">
+        <v>3000000363</v>
+      </c>
+      <c r="D3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I3">
+        <v>-4.43</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0.699873</v>
+      </c>
+      <c r="L3" s="1">
+        <v>44925</v>
+      </c>
+      <c r="M3" t="s">
+        <v>181</v>
+      </c>
+      <c r="N3" t="s">
+        <v>182</v>
+      </c>
+      <c r="O3">
+        <v>300</v>
+      </c>
+      <c r="P3" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q3">
+        <v>25</v>
+      </c>
+      <c r="R3" t="s">
+        <v>38</v>
+      </c>
+      <c r="S3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T3" t="s">
+        <v>40</v>
+      </c>
+      <c r="U3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4">
+        <v>3000000352</v>
+      </c>
+      <c r="D4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" t="s">
+        <v>179</v>
+      </c>
+      <c r="H4" t="s">
+        <v>180</v>
+      </c>
+      <c r="I4">
+        <v>1.95</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0.891507</v>
+      </c>
+      <c r="L4" s="1">
+        <v>44903</v>
+      </c>
+      <c r="M4" t="s">
+        <v>188</v>
+      </c>
+      <c r="N4" t="s">
+        <v>189</v>
+      </c>
+      <c r="O4">
+        <v>3</v>
+      </c>
+      <c r="P4" t="s">
+        <v>190</v>
+      </c>
+      <c r="R4" t="s">
+        <v>47</v>
+      </c>
+      <c r="S4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T4" t="s">
+        <v>49</v>
+      </c>
+      <c r="U4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5">
+        <v>3000000352</v>
+      </c>
+      <c r="D5" t="s">
+        <v>191</v>
+      </c>
+      <c r="E5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>185</v>
+      </c>
+      <c r="H5" t="s">
+        <v>186</v>
+      </c>
+      <c r="I5">
+        <v>-0.59</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0.891507</v>
+      </c>
+      <c r="L5" s="1">
+        <v>44903</v>
+      </c>
+      <c r="M5" t="s">
+        <v>188</v>
+      </c>
+      <c r="N5" t="s">
+        <v>189</v>
+      </c>
+      <c r="O5">
+        <v>3</v>
+      </c>
+      <c r="P5" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q5">
+        <v>30</v>
+      </c>
+      <c r="R5" t="s">
+        <v>47</v>
+      </c>
+      <c r="S5" t="s">
+        <v>48</v>
+      </c>
+      <c r="T5" t="s">
+        <v>49</v>
+      </c>
+      <c r="U5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6">
+        <v>3000000341</v>
+      </c>
+      <c r="D6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" t="s">
+        <v>192</v>
+      </c>
+      <c r="I6">
+        <v>-7.17</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>44896</v>
+      </c>
+      <c r="M6" t="s">
+        <v>182</v>
+      </c>
+      <c r="N6" t="s">
+        <v>182</v>
+      </c>
+      <c r="P6" t="s">
+        <v>182</v>
+      </c>
+      <c r="U6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>3000000330</v>
+      </c>
+      <c r="D7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" t="s">
+        <v>179</v>
+      </c>
+      <c r="H7" t="s">
+        <v>180</v>
+      </c>
+      <c r="I7">
+        <v>15.98</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0.783274</v>
+      </c>
+      <c r="L7" s="1">
+        <v>44895</v>
+      </c>
+      <c r="M7" t="s">
+        <v>194</v>
+      </c>
+      <c r="N7" t="s">
+        <v>182</v>
+      </c>
+      <c r="O7">
+        <v>300</v>
+      </c>
+      <c r="P7" t="s">
+        <v>183</v>
+      </c>
+      <c r="R7" t="s">
+        <v>38</v>
+      </c>
+      <c r="S7" t="s">
+        <v>39</v>
+      </c>
+      <c r="T7" t="s">
+        <v>40</v>
+      </c>
+      <c r="U7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8">
+        <v>3000000330</v>
+      </c>
+      <c r="D8" t="s">
+        <v>195</v>
+      </c>
+      <c r="E8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>185</v>
+      </c>
+      <c r="H8" t="s">
+        <v>186</v>
+      </c>
+      <c r="I8">
+        <v>-4</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0.783274</v>
+      </c>
+      <c r="L8" s="1">
+        <v>44895</v>
+      </c>
+      <c r="M8" t="s">
+        <v>194</v>
+      </c>
+      <c r="N8" t="s">
+        <v>182</v>
+      </c>
+      <c r="O8">
+        <v>300</v>
+      </c>
+      <c r="P8" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q8">
+        <v>25</v>
+      </c>
+      <c r="R8" t="s">
+        <v>38</v>
+      </c>
+      <c r="S8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T8" t="s">
+        <v>40</v>
+      </c>
+      <c r="U8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9">
+        <v>3000000319</v>
+      </c>
+      <c r="D9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" t="s">
+        <v>192</v>
+      </c>
+      <c r="I9">
+        <v>-7.77</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1">
+        <v>44866</v>
+      </c>
+      <c r="M9" t="s">
+        <v>182</v>
+      </c>
+      <c r="N9" t="s">
+        <v>182</v>
+      </c>
+      <c r="P9" t="s">
+        <v>182</v>
+      </c>
+      <c r="U9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10">
+        <v>3000000308</v>
+      </c>
+      <c r="D10" t="s">
+        <v>196</v>
+      </c>
+      <c r="E10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" t="s">
+        <v>179</v>
+      </c>
+      <c r="H10" t="s">
+        <v>180</v>
+      </c>
+      <c r="I10">
+        <v>16.85</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.6834</v>
+      </c>
+      <c r="L10" s="1">
+        <v>44865</v>
+      </c>
+      <c r="M10" t="s">
+        <v>197</v>
+      </c>
+      <c r="N10" t="s">
+        <v>182</v>
+      </c>
+      <c r="O10">
+        <v>300</v>
+      </c>
+      <c r="P10" t="s">
+        <v>183</v>
+      </c>
+      <c r="R10" t="s">
+        <v>38</v>
+      </c>
+      <c r="S10" t="s">
+        <v>39</v>
+      </c>
+      <c r="T10" t="s">
+        <v>40</v>
+      </c>
+      <c r="U10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11">
+        <v>3000000308</v>
+      </c>
+      <c r="D11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" t="s">
+        <v>185</v>
+      </c>
+      <c r="H11" t="s">
+        <v>186</v>
+      </c>
+      <c r="I11">
+        <v>-4.53</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0.6834</v>
+      </c>
+      <c r="L11" s="1">
+        <v>44865</v>
+      </c>
+      <c r="M11" t="s">
+        <v>197</v>
+      </c>
+      <c r="N11" t="s">
+        <v>182</v>
+      </c>
+      <c r="O11">
+        <v>300</v>
+      </c>
+      <c r="P11" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q11">
+        <v>25</v>
+      </c>
+      <c r="R11" t="s">
+        <v>38</v>
+      </c>
+      <c r="S11" t="s">
+        <v>39</v>
+      </c>
+      <c r="T11" t="s">
+        <v>40</v>
+      </c>
+      <c r="U11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12">
+        <v>3000000297</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" t="s">
+        <v>192</v>
+      </c>
+      <c r="I12">
+        <v>-8.52</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>44837</v>
+      </c>
+      <c r="M12" t="s">
+        <v>182</v>
+      </c>
+      <c r="N12" t="s">
+        <v>182</v>
+      </c>
+      <c r="P12" t="s">
+        <v>182</v>
+      </c>
+      <c r="U12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13">
+        <v>3000000286</v>
+      </c>
+      <c r="D13" t="s">
+        <v>199</v>
+      </c>
+      <c r="E13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
+        <v>179</v>
+      </c>
+      <c r="H13" t="s">
+        <v>180</v>
+      </c>
+      <c r="I13">
+        <v>18.32</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0.689236</v>
+      </c>
+      <c r="L13" s="1">
+        <v>44833</v>
+      </c>
+      <c r="M13" t="s">
+        <v>200</v>
+      </c>
+      <c r="N13" t="s">
+        <v>182</v>
+      </c>
+      <c r="O13">
+        <v>300</v>
+      </c>
+      <c r="P13" t="s">
+        <v>183</v>
+      </c>
+      <c r="R13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S13" t="s">
+        <v>39</v>
+      </c>
+      <c r="T13" t="s">
+        <v>40</v>
+      </c>
+      <c r="U13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14">
+        <v>3000000286</v>
+      </c>
+      <c r="D14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" t="s">
+        <v>185</v>
+      </c>
+      <c r="H14" t="s">
+        <v>186</v>
+      </c>
+      <c r="I14">
+        <v>-4.58</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0.689236</v>
+      </c>
+      <c r="L14" s="1">
+        <v>44833</v>
+      </c>
+      <c r="M14" t="s">
+        <v>200</v>
+      </c>
+      <c r="N14" t="s">
+        <v>182</v>
+      </c>
+      <c r="O14">
+        <v>300</v>
+      </c>
+      <c r="P14" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q14">
+        <v>25</v>
+      </c>
+      <c r="R14" t="s">
+        <v>38</v>
+      </c>
+      <c r="S14" t="s">
+        <v>39</v>
+      </c>
+      <c r="T14" t="s">
+        <v>40</v>
+      </c>
+      <c r="U14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15">
+        <v>3000000275</v>
+      </c>
+      <c r="D15" t="s">
+        <v>202</v>
+      </c>
+      <c r="E15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" t="s">
+        <v>185</v>
+      </c>
+      <c r="H15" t="s">
+        <v>186</v>
+      </c>
+      <c r="I15">
+        <v>-0.6</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>1.047325</v>
+      </c>
+      <c r="L15" s="1">
+        <v>44812</v>
+      </c>
+      <c r="M15" t="s">
+        <v>203</v>
+      </c>
+      <c r="N15" t="s">
+        <v>204</v>
+      </c>
+      <c r="O15">
+        <v>3</v>
+      </c>
+      <c r="P15" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q15">
+        <v>30</v>
+      </c>
+      <c r="R15" t="s">
+        <v>47</v>
+      </c>
+      <c r="S15" t="s">
+        <v>48</v>
+      </c>
+      <c r="T15" t="s">
+        <v>49</v>
+      </c>
+      <c r="U15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
+      <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16">
+        <v>3000000275</v>
+      </c>
+      <c r="D16" t="s">
+        <v>205</v>
+      </c>
+      <c r="E16" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" t="s">
+        <v>179</v>
+      </c>
+      <c r="H16" t="s">
+        <v>180</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>1.047325</v>
+      </c>
+      <c r="L16" s="1">
+        <v>44812</v>
+      </c>
+      <c r="M16" t="s">
+        <v>203</v>
+      </c>
+      <c r="N16" t="s">
+        <v>204</v>
+      </c>
+      <c r="O16">
+        <v>3</v>
+      </c>
+      <c r="P16" t="s">
+        <v>206</v>
+      </c>
+      <c r="R16" t="s">
+        <v>47</v>
+      </c>
+      <c r="S16" t="s">
+        <v>48</v>
+      </c>
+      <c r="T16" t="s">
+        <v>49</v>
+      </c>
+      <c r="U16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
+      <c r="A17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" t="s">
+        <v>192</v>
+      </c>
+      <c r="I17">
+        <v>-8.3</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1">
+        <v>44806</v>
+      </c>
+      <c r="M17" t="s">
+        <v>182</v>
+      </c>
+      <c r="N17" t="s">
+        <v>182</v>
+      </c>
+      <c r="P17" t="s">
+        <v>182</v>
+      </c>
+      <c r="U17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
+      <c r="A18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18">
+        <v>3000000264</v>
+      </c>
+      <c r="D18" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" t="s">
+        <v>67</v>
+      </c>
+      <c r="G18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H18" t="s">
+        <v>207</v>
+      </c>
+      <c r="I18">
+        <v>0.59</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>1.044204</v>
+      </c>
+      <c r="L18" s="1">
+        <v>44805</v>
+      </c>
+      <c r="M18" t="s">
+        <v>182</v>
+      </c>
+      <c r="N18" t="s">
+        <v>182</v>
+      </c>
+      <c r="P18" t="s">
+        <v>182</v>
+      </c>
+      <c r="U18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19">
+        <v>3000000253</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" t="s">
+        <v>67</v>
+      </c>
+      <c r="G19" t="s">
+        <v>67</v>
+      </c>
+      <c r="H19" t="s">
+        <v>207</v>
+      </c>
+      <c r="I19">
+        <v>1.13</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0.703145</v>
+      </c>
+      <c r="L19" s="1">
+        <v>44805</v>
+      </c>
+      <c r="M19" t="s">
+        <v>182</v>
+      </c>
+      <c r="N19" t="s">
+        <v>182</v>
+      </c>
+      <c r="P19" t="s">
+        <v>182</v>
+      </c>
+      <c r="U19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20">
+        <v>3000000242</v>
+      </c>
+      <c r="D20" t="s">
+        <v>208</v>
+      </c>
+      <c r="E20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" t="s">
+        <v>179</v>
+      </c>
+      <c r="H20" t="s">
+        <v>180</v>
+      </c>
+      <c r="I20">
+        <v>18.7</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0.704849</v>
+      </c>
+      <c r="L20" s="1">
+        <v>44804</v>
+      </c>
+      <c r="M20" t="s">
+        <v>209</v>
+      </c>
+      <c r="N20" t="s">
+        <v>182</v>
+      </c>
+      <c r="O20">
+        <v>300</v>
+      </c>
+      <c r="P20" t="s">
+        <v>183</v>
+      </c>
+      <c r="R20" t="s">
+        <v>38</v>
+      </c>
+      <c r="S20" t="s">
+        <v>39</v>
+      </c>
+      <c r="T20" t="s">
+        <v>40</v>
+      </c>
+      <c r="U20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21">
+        <v>3000000242</v>
+      </c>
+      <c r="D21" t="s">
+        <v>210</v>
+      </c>
+      <c r="E21" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" t="s">
+        <v>185</v>
+      </c>
+      <c r="H21" t="s">
+        <v>186</v>
+      </c>
+      <c r="I21">
+        <v>-4.44</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0.704849</v>
+      </c>
+      <c r="L21" s="1">
+        <v>44804</v>
+      </c>
+      <c r="M21" t="s">
+        <v>209</v>
+      </c>
+      <c r="N21" t="s">
+        <v>182</v>
+      </c>
+      <c r="O21">
+        <v>300</v>
+      </c>
+      <c r="P21" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q21">
+        <v>25</v>
+      </c>
+      <c r="R21" t="s">
+        <v>38</v>
+      </c>
+      <c r="S21" t="s">
+        <v>39</v>
+      </c>
+      <c r="T21" t="s">
+        <v>40</v>
+      </c>
+      <c r="U21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
+      <c r="A22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22">
+        <v>3000000231</v>
+      </c>
+      <c r="D22" t="s">
+        <v>211</v>
+      </c>
+      <c r="E22" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" t="s">
+        <v>212</v>
+      </c>
+      <c r="H22" t="s">
+        <v>213</v>
+      </c>
+      <c r="I22">
+        <v>0.56</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1">
+        <v>44788</v>
+      </c>
+      <c r="M22" t="s">
+        <v>214</v>
+      </c>
+      <c r="N22" t="s">
+        <v>182</v>
+      </c>
+      <c r="O22">
+        <v>3</v>
+      </c>
+      <c r="P22" t="s">
+        <v>182</v>
+      </c>
+      <c r="R22" t="s">
+        <v>80</v>
+      </c>
+      <c r="S22" t="s">
+        <v>81</v>
+      </c>
+      <c r="T22" t="s">
+        <v>82</v>
+      </c>
+      <c r="U22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
+      <c r="A23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23">
+        <v>3000000231</v>
+      </c>
+      <c r="D23" t="s">
+        <v>215</v>
+      </c>
+      <c r="E23" t="s">
+        <v>78</v>
+      </c>
+      <c r="F23" t="s">
+        <v>79</v>
+      </c>
+      <c r="G23" t="s">
+        <v>185</v>
+      </c>
+      <c r="H23" t="s">
+        <v>186</v>
+      </c>
+      <c r="I23">
+        <v>-0.09</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1">
+        <v>44788</v>
+      </c>
+      <c r="M23" t="s">
+        <v>214</v>
+      </c>
+      <c r="N23" t="s">
+        <v>182</v>
+      </c>
+      <c r="O23">
+        <v>3</v>
+      </c>
+      <c r="P23" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q23">
+        <v>15</v>
+      </c>
+      <c r="R23" t="s">
+        <v>80</v>
+      </c>
+      <c r="S23" t="s">
+        <v>81</v>
+      </c>
+      <c r="T23" t="s">
+        <v>82</v>
+      </c>
+      <c r="U23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24">
+        <v>3000000220</v>
+      </c>
+      <c r="D24" t="s">
+        <v>216</v>
+      </c>
+      <c r="E24" t="s">
+        <v>84</v>
+      </c>
+      <c r="F24" t="s">
+        <v>79</v>
+      </c>
+      <c r="G24" t="s">
+        <v>185</v>
+      </c>
+      <c r="H24" t="s">
+        <v>186</v>
+      </c>
+      <c r="I24">
+        <v>-0.03</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1">
+        <v>44777</v>
+      </c>
+      <c r="M24" t="s">
+        <v>217</v>
+      </c>
+      <c r="N24" t="s">
+        <v>218</v>
+      </c>
+      <c r="O24">
+        <v>3</v>
+      </c>
+      <c r="P24" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q24">
+        <v>15</v>
+      </c>
+      <c r="R24" t="s">
+        <v>85</v>
+      </c>
+      <c r="S24" t="s">
+        <v>86</v>
+      </c>
+      <c r="T24" t="s">
+        <v>87</v>
+      </c>
+      <c r="U24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="A25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25">
+        <v>3000000220</v>
+      </c>
+      <c r="D25" t="s">
+        <v>219</v>
+      </c>
+      <c r="E25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F25" t="s">
+        <v>79</v>
+      </c>
+      <c r="G25" t="s">
+        <v>212</v>
+      </c>
+      <c r="H25" t="s">
+        <v>213</v>
+      </c>
+      <c r="I25">
+        <v>0.16</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1">
+        <v>44777</v>
+      </c>
+      <c r="M25" t="s">
+        <v>217</v>
+      </c>
+      <c r="N25" t="s">
+        <v>218</v>
+      </c>
+      <c r="O25">
+        <v>3</v>
+      </c>
+      <c r="P25" t="s">
+        <v>182</v>
+      </c>
+      <c r="R25" t="s">
+        <v>85</v>
+      </c>
+      <c r="S25" t="s">
+        <v>86</v>
+      </c>
+      <c r="T25" t="s">
+        <v>87</v>
+      </c>
+      <c r="U25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
+      <c r="A26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26">
+        <v>3000000209</v>
+      </c>
+      <c r="D26" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" t="s">
+        <v>67</v>
+      </c>
+      <c r="G26" t="s">
+        <v>67</v>
+      </c>
+      <c r="H26" t="s">
+        <v>207</v>
+      </c>
+      <c r="I26">
+        <v>0.4</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0.971475</v>
+      </c>
+      <c r="L26" s="1">
+        <v>44774</v>
+      </c>
+      <c r="M26" t="s">
+        <v>182</v>
+      </c>
+      <c r="N26" t="s">
+        <v>182</v>
+      </c>
+      <c r="P26" t="s">
+        <v>182</v>
+      </c>
+      <c r="U26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
+      <c r="A27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27">
+        <v>3000000198</v>
+      </c>
+      <c r="D27" t="s">
+        <v>90</v>
+      </c>
+      <c r="F27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G27" t="s">
+        <v>67</v>
+      </c>
+      <c r="H27" t="s">
+        <v>207</v>
+      </c>
+      <c r="I27">
+        <v>0.63</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0.789892</v>
+      </c>
+      <c r="L27" s="1">
+        <v>44774</v>
+      </c>
+      <c r="M27" t="s">
+        <v>182</v>
+      </c>
+      <c r="N27" t="s">
+        <v>182</v>
+      </c>
+      <c r="P27" t="s">
+        <v>182</v>
+      </c>
+      <c r="U27" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" t="s">
+        <v>91</v>
+      </c>
+      <c r="F28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" t="s">
+        <v>54</v>
+      </c>
+      <c r="H28" t="s">
+        <v>192</v>
+      </c>
+      <c r="I28">
+        <v>-8.73</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1">
+        <v>44774</v>
+      </c>
+      <c r="M28" t="s">
+        <v>182</v>
+      </c>
+      <c r="N28" t="s">
+        <v>182</v>
+      </c>
+      <c r="P28" t="s">
+        <v>182</v>
+      </c>
+      <c r="U28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
+      <c r="A29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29">
+        <v>3000000187</v>
+      </c>
+      <c r="D29" t="s">
+        <v>220</v>
+      </c>
+      <c r="E29" t="s">
+        <v>92</v>
+      </c>
+      <c r="F29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G29" t="s">
+        <v>179</v>
+      </c>
+      <c r="H29" t="s">
+        <v>180</v>
+      </c>
+      <c r="I29">
+        <v>16.63</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0.8111</v>
+      </c>
+      <c r="L29" s="1">
+        <v>44771</v>
+      </c>
+      <c r="M29" t="s">
+        <v>221</v>
+      </c>
+      <c r="N29" t="s">
+        <v>182</v>
+      </c>
+      <c r="O29">
+        <v>300</v>
+      </c>
+      <c r="P29" t="s">
+        <v>183</v>
+      </c>
+      <c r="R29" t="s">
+        <v>38</v>
+      </c>
+      <c r="S29" t="s">
+        <v>39</v>
+      </c>
+      <c r="T29" t="s">
+        <v>40</v>
+      </c>
+      <c r="U29" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
+      <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30">
+        <v>3000000187</v>
+      </c>
+      <c r="D30" t="s">
+        <v>222</v>
+      </c>
+      <c r="E30" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" t="s">
+        <v>35</v>
+      </c>
+      <c r="G30" t="s">
+        <v>185</v>
+      </c>
+      <c r="H30" t="s">
+        <v>186</v>
+      </c>
+      <c r="I30">
+        <v>-4.71</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0.8111</v>
+      </c>
+      <c r="L30" s="1">
+        <v>44771</v>
+      </c>
+      <c r="M30" t="s">
+        <v>221</v>
+      </c>
+      <c r="N30" t="s">
+        <v>182</v>
+      </c>
+      <c r="O30">
+        <v>300</v>
+      </c>
+      <c r="P30" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q30">
+        <v>25</v>
+      </c>
+      <c r="R30" t="s">
+        <v>38</v>
+      </c>
+      <c r="S30" t="s">
+        <v>39</v>
+      </c>
+      <c r="T30" t="s">
+        <v>40</v>
+      </c>
+      <c r="U30" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
+      <c r="A31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" t="s">
+        <v>93</v>
+      </c>
+      <c r="F31" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H31" t="s">
+        <v>192</v>
+      </c>
+      <c r="I31">
+        <v>-7.87</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31" s="1">
+        <v>44747</v>
+      </c>
+      <c r="M31" t="s">
+        <v>182</v>
+      </c>
+      <c r="N31" t="s">
+        <v>182</v>
+      </c>
+      <c r="P31" t="s">
+        <v>182</v>
+      </c>
+      <c r="U31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
+      <c r="A32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32">
+        <v>3000000176</v>
+      </c>
+      <c r="D32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F32" t="s">
+        <v>67</v>
+      </c>
+      <c r="G32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H32" t="s">
+        <v>207</v>
+      </c>
+      <c r="I32">
+        <v>0.06</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>1.024197</v>
+      </c>
+      <c r="L32" s="1">
+        <v>44743</v>
+      </c>
+      <c r="M32" t="s">
+        <v>182</v>
+      </c>
+      <c r="N32" t="s">
+        <v>182</v>
+      </c>
+      <c r="P32" t="s">
+        <v>182</v>
+      </c>
+      <c r="U32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33">
+        <v>3000000165</v>
+      </c>
+      <c r="D33" t="s">
+        <v>96</v>
+      </c>
+      <c r="F33" t="s">
+        <v>67</v>
+      </c>
+      <c r="G33" t="s">
+        <v>67</v>
+      </c>
+      <c r="H33" t="s">
+        <v>207</v>
+      </c>
+      <c r="I33">
+        <v>0.2</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0.754441</v>
+      </c>
+      <c r="L33" s="1">
+        <v>44743</v>
+      </c>
+      <c r="M33" t="s">
+        <v>182</v>
+      </c>
+      <c r="N33" t="s">
+        <v>182</v>
+      </c>
+      <c r="P33" t="s">
+        <v>182</v>
+      </c>
+      <c r="U33" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34">
+        <v>3000000154</v>
+      </c>
+      <c r="D34" t="s">
+        <v>223</v>
+      </c>
+      <c r="E34" t="s">
+        <v>97</v>
+      </c>
+      <c r="F34" t="s">
+        <v>35</v>
+      </c>
+      <c r="G34" t="s">
+        <v>179</v>
+      </c>
+      <c r="H34" t="s">
+        <v>180</v>
+      </c>
+      <c r="I34">
+        <v>18.02</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0.767365</v>
+      </c>
+      <c r="L34" s="1">
+        <v>44742</v>
+      </c>
+      <c r="M34" t="s">
+        <v>224</v>
+      </c>
+      <c r="N34" t="s">
+        <v>182</v>
+      </c>
+      <c r="O34">
+        <v>300</v>
+      </c>
+      <c r="P34" t="s">
+        <v>183</v>
+      </c>
+      <c r="R34" t="s">
+        <v>38</v>
+      </c>
+      <c r="S34" t="s">
+        <v>39</v>
+      </c>
+      <c r="T34" t="s">
+        <v>40</v>
+      </c>
+      <c r="U34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
+      <c r="A35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35">
+        <v>3000000154</v>
+      </c>
+      <c r="D35" t="s">
+        <v>225</v>
+      </c>
+      <c r="E35" t="s">
+        <v>97</v>
+      </c>
+      <c r="F35" t="s">
+        <v>35</v>
+      </c>
+      <c r="G35" t="s">
+        <v>185</v>
+      </c>
+      <c r="H35" t="s">
+        <v>186</v>
+      </c>
+      <c r="I35">
+        <v>-4.46</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0.767365</v>
+      </c>
+      <c r="L35" s="1">
+        <v>44742</v>
+      </c>
+      <c r="M35" t="s">
+        <v>224</v>
+      </c>
+      <c r="N35" t="s">
+        <v>182</v>
+      </c>
+      <c r="O35">
+        <v>300</v>
+      </c>
+      <c r="P35" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q35">
+        <v>25</v>
+      </c>
+      <c r="R35" t="s">
+        <v>38</v>
+      </c>
+      <c r="S35" t="s">
+        <v>39</v>
+      </c>
+      <c r="T35" t="s">
+        <v>40</v>
+      </c>
+      <c r="U35" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
+      <c r="A36" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36">
+        <v>3000000143</v>
+      </c>
+      <c r="D36" t="s">
+        <v>226</v>
+      </c>
+      <c r="E36" t="s">
+        <v>98</v>
+      </c>
+      <c r="F36" t="s">
+        <v>35</v>
+      </c>
+      <c r="G36" t="s">
+        <v>179</v>
+      </c>
+      <c r="H36" t="s">
+        <v>180</v>
+      </c>
+      <c r="I36">
+        <v>1.66</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0.94887</v>
+      </c>
+      <c r="L36" s="1">
+        <v>44721</v>
+      </c>
+      <c r="M36" t="s">
+        <v>227</v>
+      </c>
+      <c r="N36" t="s">
+        <v>228</v>
+      </c>
+      <c r="O36">
+        <v>3</v>
+      </c>
+      <c r="P36" t="s">
+        <v>206</v>
+      </c>
+      <c r="R36" t="s">
+        <v>47</v>
+      </c>
+      <c r="S36" t="s">
+        <v>48</v>
+      </c>
+      <c r="T36" t="s">
+        <v>49</v>
+      </c>
+      <c r="U36" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
+      <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37">
+        <v>3000000143</v>
+      </c>
+      <c r="D37" t="s">
+        <v>229</v>
+      </c>
+      <c r="E37" t="s">
+        <v>98</v>
+      </c>
+      <c r="F37" t="s">
+        <v>35</v>
+      </c>
+      <c r="G37" t="s">
+        <v>185</v>
+      </c>
+      <c r="H37" t="s">
+        <v>186</v>
+      </c>
+      <c r="I37">
+        <v>-0.5</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0.94887</v>
+      </c>
+      <c r="L37" s="1">
+        <v>44721</v>
+      </c>
+      <c r="M37" t="s">
+        <v>227</v>
+      </c>
+      <c r="N37" t="s">
+        <v>228</v>
+      </c>
+      <c r="O37">
+        <v>3</v>
+      </c>
+      <c r="P37" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q37">
+        <v>30</v>
+      </c>
+      <c r="R37" t="s">
+        <v>47</v>
+      </c>
+      <c r="S37" t="s">
+        <v>48</v>
+      </c>
+      <c r="T37" t="s">
+        <v>49</v>
+      </c>
+      <c r="U37" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21">
+      <c r="A38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38">
+        <v>3000000132</v>
+      </c>
+      <c r="D38" t="s">
+        <v>230</v>
+      </c>
+      <c r="E38" t="s">
+        <v>99</v>
+      </c>
+      <c r="F38" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" t="s">
+        <v>212</v>
+      </c>
+      <c r="H38" t="s">
+        <v>213</v>
+      </c>
+      <c r="I38">
+        <v>2.15</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="L38" s="1">
+        <v>44721</v>
+      </c>
+      <c r="M38" t="s">
+        <v>231</v>
+      </c>
+      <c r="N38" t="s">
+        <v>182</v>
+      </c>
+      <c r="O38">
+        <v>30</v>
+      </c>
+      <c r="P38" t="s">
+        <v>182</v>
+      </c>
+      <c r="R38" t="s">
+        <v>101</v>
+      </c>
+      <c r="S38" t="s">
+        <v>102</v>
+      </c>
+      <c r="T38" t="s">
+        <v>103</v>
+      </c>
+      <c r="U38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
+      <c r="A39" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" t="s">
+        <v>105</v>
+      </c>
+      <c r="F39" t="s">
+        <v>54</v>
+      </c>
+      <c r="G39" t="s">
+        <v>54</v>
+      </c>
+      <c r="H39" t="s">
+        <v>192</v>
+      </c>
+      <c r="I39">
+        <v>-8.73</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39" s="1">
+        <v>44713</v>
+      </c>
+      <c r="M39" t="s">
+        <v>182</v>
+      </c>
+      <c r="N39" t="s">
+        <v>182</v>
+      </c>
+      <c r="P39" t="s">
+        <v>182</v>
+      </c>
+      <c r="U39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
+      <c r="A40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40">
+        <v>3000000121</v>
+      </c>
+      <c r="D40" t="s">
+        <v>232</v>
+      </c>
+      <c r="E40" t="s">
+        <v>106</v>
+      </c>
+      <c r="F40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G40" t="s">
+        <v>179</v>
+      </c>
+      <c r="H40" t="s">
+        <v>180</v>
+      </c>
+      <c r="I40">
+        <v>18.59</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0.707732</v>
+      </c>
+      <c r="L40" s="1">
+        <v>44712</v>
+      </c>
+      <c r="M40" t="s">
+        <v>231</v>
+      </c>
+      <c r="N40" t="s">
+        <v>182</v>
+      </c>
+      <c r="O40">
+        <v>300</v>
+      </c>
+      <c r="P40" t="s">
+        <v>183</v>
+      </c>
+      <c r="R40" t="s">
+        <v>38</v>
+      </c>
+      <c r="S40" t="s">
+        <v>39</v>
+      </c>
+      <c r="T40" t="s">
+        <v>40</v>
+      </c>
+      <c r="U40" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
+      <c r="A41" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41">
+        <v>3000000121</v>
+      </c>
+      <c r="D41" t="s">
+        <v>233</v>
+      </c>
+      <c r="E41" t="s">
+        <v>106</v>
+      </c>
+      <c r="F41" t="s">
+        <v>35</v>
+      </c>
+      <c r="G41" t="s">
+        <v>185</v>
+      </c>
+      <c r="H41" t="s">
+        <v>186</v>
+      </c>
+      <c r="I41">
+        <v>-4.65</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0.707732</v>
+      </c>
+      <c r="L41" s="1">
+        <v>44712</v>
+      </c>
+      <c r="M41" t="s">
+        <v>231</v>
+      </c>
+      <c r="N41" t="s">
+        <v>182</v>
+      </c>
+      <c r="O41">
+        <v>300</v>
+      </c>
+      <c r="P41" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q41">
+        <v>25</v>
+      </c>
+      <c r="R41" t="s">
+        <v>38</v>
+      </c>
+      <c r="S41" t="s">
+        <v>39</v>
+      </c>
+      <c r="T41" t="s">
+        <v>40</v>
+      </c>
+      <c r="U41" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
+      <c r="A42" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42">
+        <v>3000000110</v>
+      </c>
+      <c r="D42" t="s">
+        <v>234</v>
+      </c>
+      <c r="E42" t="s">
+        <v>107</v>
+      </c>
+      <c r="F42" t="s">
+        <v>35</v>
+      </c>
+      <c r="G42" t="s">
+        <v>179</v>
+      </c>
+      <c r="H42" t="s">
+        <v>180</v>
+      </c>
+      <c r="I42">
+        <v>4.95</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42" s="1">
+        <v>44711</v>
+      </c>
+      <c r="M42" t="s">
+        <v>235</v>
+      </c>
+      <c r="N42" t="s">
+        <v>227</v>
+      </c>
+      <c r="O42">
+        <v>4</v>
+      </c>
+      <c r="P42" t="s">
+        <v>236</v>
+      </c>
+      <c r="R42" t="s">
+        <v>108</v>
+      </c>
+      <c r="S42" t="s">
+        <v>109</v>
+      </c>
+      <c r="T42" t="s">
+        <v>110</v>
+      </c>
+      <c r="U42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
+      <c r="A43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43">
+        <v>3000000110</v>
+      </c>
+      <c r="D43" t="s">
+        <v>237</v>
+      </c>
+      <c r="E43" t="s">
+        <v>107</v>
+      </c>
+      <c r="F43" t="s">
+        <v>35</v>
+      </c>
+      <c r="G43" t="s">
+        <v>185</v>
+      </c>
+      <c r="H43" t="s">
+        <v>186</v>
+      </c>
+      <c r="I43">
+        <v>-0.74</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="L43" s="1">
+        <v>44711</v>
+      </c>
+      <c r="M43" t="s">
+        <v>235</v>
+      </c>
+      <c r="N43" t="s">
+        <v>227</v>
+      </c>
+      <c r="O43">
+        <v>4</v>
+      </c>
+      <c r="P43" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q43">
+        <v>15</v>
+      </c>
+      <c r="R43" t="s">
+        <v>108</v>
+      </c>
+      <c r="S43" t="s">
+        <v>109</v>
+      </c>
+      <c r="T43" t="s">
+        <v>110</v>
+      </c>
+      <c r="U43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21">
+      <c r="A44" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44">
+        <v>3000000099</v>
+      </c>
+      <c r="D44" t="s">
+        <v>238</v>
+      </c>
+      <c r="E44" t="s">
+        <v>113</v>
+      </c>
+      <c r="F44" t="s">
+        <v>79</v>
+      </c>
+      <c r="G44" t="s">
+        <v>185</v>
+      </c>
+      <c r="H44" t="s">
+        <v>186</v>
+      </c>
+      <c r="I44">
+        <v>-0.2</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>1</v>
+      </c>
+      <c r="L44" s="1">
+        <v>44699</v>
+      </c>
+      <c r="M44" t="s">
+        <v>239</v>
+      </c>
+      <c r="N44" t="s">
+        <v>182</v>
+      </c>
+      <c r="O44">
+        <v>3</v>
+      </c>
+      <c r="P44" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q44">
+        <v>15</v>
+      </c>
+      <c r="R44" t="s">
+        <v>80</v>
+      </c>
+      <c r="S44" t="s">
+        <v>81</v>
+      </c>
+      <c r="T44" t="s">
+        <v>82</v>
+      </c>
+      <c r="U44" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21">
+      <c r="A45" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45">
+        <v>3000000099</v>
+      </c>
+      <c r="D45" t="s">
+        <v>240</v>
+      </c>
+      <c r="E45" t="s">
+        <v>113</v>
+      </c>
+      <c r="F45" t="s">
+        <v>79</v>
+      </c>
+      <c r="G45" t="s">
+        <v>212</v>
+      </c>
+      <c r="H45" t="s">
+        <v>213</v>
+      </c>
+      <c r="I45">
+        <v>0.9</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="L45" s="1">
+        <v>44699</v>
+      </c>
+      <c r="M45" t="s">
+        <v>239</v>
+      </c>
+      <c r="N45" t="s">
+        <v>182</v>
+      </c>
+      <c r="O45">
+        <v>3</v>
+      </c>
+      <c r="P45" t="s">
+        <v>182</v>
+      </c>
+      <c r="R45" t="s">
+        <v>80</v>
+      </c>
+      <c r="S45" t="s">
+        <v>81</v>
+      </c>
+      <c r="T45" t="s">
+        <v>82</v>
+      </c>
+      <c r="U45" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
+      <c r="A46" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46">
+        <v>3000000088</v>
+      </c>
+      <c r="D46" t="s">
+        <v>241</v>
+      </c>
+      <c r="E46" t="s">
+        <v>114</v>
+      </c>
+      <c r="F46" t="s">
+        <v>79</v>
+      </c>
+      <c r="G46" t="s">
+        <v>212</v>
+      </c>
+      <c r="H46" t="s">
+        <v>213</v>
+      </c>
+      <c r="I46">
+        <v>1.14</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="L46" s="1">
+        <v>44690</v>
+      </c>
+      <c r="M46" t="s">
+        <v>242</v>
+      </c>
+      <c r="N46" t="s">
+        <v>243</v>
+      </c>
+      <c r="O46">
+        <v>3</v>
+      </c>
+      <c r="P46" t="s">
+        <v>182</v>
+      </c>
+      <c r="R46" t="s">
+        <v>80</v>
+      </c>
+      <c r="S46" t="s">
+        <v>81</v>
+      </c>
+      <c r="T46" t="s">
+        <v>82</v>
+      </c>
+      <c r="U46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21">
+      <c r="A47" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47">
+        <v>3000000088</v>
+      </c>
+      <c r="D47" t="s">
+        <v>244</v>
+      </c>
+      <c r="E47" t="s">
+        <v>114</v>
+      </c>
+      <c r="F47" t="s">
+        <v>79</v>
+      </c>
+      <c r="G47" t="s">
+        <v>185</v>
+      </c>
+      <c r="H47" t="s">
+        <v>186</v>
+      </c>
+      <c r="I47">
+        <v>-0.17</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>1</v>
+      </c>
+      <c r="L47" s="1">
+        <v>44690</v>
+      </c>
+      <c r="M47" t="s">
+        <v>242</v>
+      </c>
+      <c r="N47" t="s">
+        <v>243</v>
+      </c>
+      <c r="O47">
+        <v>3</v>
+      </c>
+      <c r="P47" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q47">
+        <v>15</v>
+      </c>
+      <c r="R47" t="s">
+        <v>80</v>
+      </c>
+      <c r="S47" t="s">
+        <v>81</v>
+      </c>
+      <c r="T47" t="s">
+        <v>82</v>
+      </c>
+      <c r="U47" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21">
+      <c r="A48" t="s">
+        <v>51</v>
+      </c>
+      <c r="D48" t="s">
+        <v>115</v>
+      </c>
+      <c r="F48" t="s">
+        <v>54</v>
+      </c>
+      <c r="G48" t="s">
+        <v>54</v>
+      </c>
+      <c r="H48" t="s">
+        <v>192</v>
+      </c>
+      <c r="I48">
+        <v>-7.79</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>1</v>
+      </c>
+      <c r="L48" s="1">
+        <v>44683</v>
+      </c>
+      <c r="M48" t="s">
+        <v>182</v>
+      </c>
+      <c r="N48" t="s">
+        <v>182</v>
+      </c>
+      <c r="P48" t="s">
+        <v>182</v>
+      </c>
+      <c r="U48" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21">
+      <c r="A49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49">
+        <v>3000000077</v>
+      </c>
+      <c r="D49" t="s">
+        <v>245</v>
+      </c>
+      <c r="E49" t="s">
+        <v>116</v>
+      </c>
+      <c r="F49" t="s">
+        <v>35</v>
+      </c>
+      <c r="G49" t="s">
+        <v>179</v>
+      </c>
+      <c r="H49" t="s">
+        <v>180</v>
+      </c>
+      <c r="I49">
+        <v>19.01</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0.748283</v>
+      </c>
+      <c r="L49" s="1">
+        <v>44680</v>
+      </c>
+      <c r="M49" t="s">
+        <v>246</v>
+      </c>
+      <c r="N49" t="s">
+        <v>182</v>
+      </c>
+      <c r="O49">
+        <v>300</v>
+      </c>
+      <c r="P49" t="s">
+        <v>183</v>
+      </c>
+      <c r="R49" t="s">
+        <v>38</v>
+      </c>
+      <c r="S49" t="s">
+        <v>39</v>
+      </c>
+      <c r="T49" t="s">
+        <v>40</v>
+      </c>
+      <c r="U49" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21">
+      <c r="A50" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50">
+        <v>3000000077</v>
+      </c>
+      <c r="D50" t="s">
+        <v>247</v>
+      </c>
+      <c r="E50" t="s">
+        <v>116</v>
+      </c>
+      <c r="F50" t="s">
+        <v>35</v>
+      </c>
+      <c r="G50" t="s">
+        <v>185</v>
+      </c>
+      <c r="H50" t="s">
+        <v>186</v>
+      </c>
+      <c r="I50">
+        <v>-4.76</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0.748283</v>
+      </c>
+      <c r="L50" s="1">
+        <v>44680</v>
+      </c>
+      <c r="M50" t="s">
+        <v>246</v>
+      </c>
+      <c r="N50" t="s">
+        <v>182</v>
+      </c>
+      <c r="O50">
+        <v>300</v>
+      </c>
+      <c r="P50" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q50">
+        <v>25</v>
+      </c>
+      <c r="R50" t="s">
+        <v>38</v>
+      </c>
+      <c r="S50" t="s">
+        <v>39</v>
+      </c>
+      <c r="T50" t="s">
+        <v>40</v>
+      </c>
+      <c r="U50" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+      <c r="C51">
+        <v>3000000066</v>
+      </c>
+      <c r="D51" t="s">
+        <v>248</v>
+      </c>
+      <c r="E51" t="s">
+        <v>117</v>
+      </c>
+      <c r="F51" t="s">
+        <v>79</v>
+      </c>
+      <c r="G51" t="s">
+        <v>185</v>
+      </c>
+      <c r="H51" t="s">
+        <v>186</v>
+      </c>
+      <c r="I51">
+        <v>-0.05</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>1</v>
+      </c>
+      <c r="L51" s="1">
+        <v>44673</v>
+      </c>
+      <c r="M51" t="s">
+        <v>249</v>
+      </c>
+      <c r="N51" t="s">
+        <v>250</v>
+      </c>
+      <c r="O51">
+        <v>3</v>
+      </c>
+      <c r="P51" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q51">
+        <v>15</v>
+      </c>
+      <c r="R51" t="s">
+        <v>85</v>
+      </c>
+      <c r="S51" t="s">
+        <v>86</v>
+      </c>
+      <c r="T51" t="s">
+        <v>87</v>
+      </c>
+      <c r="U51" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21">
+      <c r="A52" t="s">
+        <v>51</v>
+      </c>
+      <c r="C52">
+        <v>3000000066</v>
+      </c>
+      <c r="D52" t="s">
+        <v>251</v>
+      </c>
+      <c r="E52" t="s">
+        <v>117</v>
+      </c>
+      <c r="F52" t="s">
+        <v>79</v>
+      </c>
+      <c r="G52" t="s">
+        <v>212</v>
+      </c>
+      <c r="H52" t="s">
+        <v>213</v>
+      </c>
+      <c r="I52">
+        <v>0.26</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>1</v>
+      </c>
+      <c r="L52" s="1">
+        <v>44673</v>
+      </c>
+      <c r="M52" t="s">
+        <v>249</v>
+      </c>
+      <c r="N52" t="s">
+        <v>250</v>
+      </c>
+      <c r="O52">
+        <v>3</v>
+      </c>
+      <c r="P52" t="s">
+        <v>182</v>
+      </c>
+      <c r="R52" t="s">
+        <v>85</v>
+      </c>
+      <c r="S52" t="s">
+        <v>86</v>
+      </c>
+      <c r="T52" t="s">
+        <v>87</v>
+      </c>
+      <c r="U52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21">
+      <c r="A53" t="s">
+        <v>44</v>
+      </c>
+      <c r="B53" t="s">
+        <v>118</v>
+      </c>
+      <c r="C53">
+        <v>3000000055</v>
+      </c>
+      <c r="D53" t="s">
+        <v>252</v>
+      </c>
+      <c r="F53" t="s">
+        <v>121</v>
+      </c>
+      <c r="G53" t="s">
+        <v>253</v>
+      </c>
+      <c r="H53" t="s">
+        <v>254</v>
+      </c>
+      <c r="I53">
+        <v>-190.52</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0.905853</v>
+      </c>
+      <c r="L53" s="1">
+        <v>44655</v>
+      </c>
+      <c r="M53" t="s">
+        <v>182</v>
+      </c>
+      <c r="N53" t="s">
+        <v>182</v>
+      </c>
+      <c r="P53" t="s">
+        <v>182</v>
+      </c>
+      <c r="R53" t="s">
+        <v>122</v>
+      </c>
+      <c r="S53" t="s">
+        <v>123</v>
+      </c>
+      <c r="T53" t="s">
+        <v>124</v>
+      </c>
+      <c r="U53" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21">
+      <c r="A54" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" t="s">
+        <v>118</v>
+      </c>
+      <c r="C54">
+        <v>3000000055</v>
+      </c>
+      <c r="D54" t="s">
+        <v>255</v>
+      </c>
+      <c r="F54" t="s">
+        <v>121</v>
+      </c>
+      <c r="G54" t="s">
+        <v>256</v>
+      </c>
+      <c r="H54" t="s">
+        <v>257</v>
+      </c>
+      <c r="I54">
+        <v>-6.59</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0.905853</v>
+      </c>
+      <c r="L54" s="1">
+        <v>44655</v>
+      </c>
+      <c r="M54" t="s">
+        <v>182</v>
+      </c>
+      <c r="N54" t="s">
+        <v>182</v>
+      </c>
+      <c r="P54" t="s">
+        <v>182</v>
+      </c>
+      <c r="R54" t="s">
+        <v>122</v>
+      </c>
+      <c r="S54" t="s">
+        <v>123</v>
+      </c>
+      <c r="T54" t="s">
+        <v>124</v>
+      </c>
+      <c r="U54" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21">
+      <c r="A55" t="s">
+        <v>51</v>
+      </c>
+      <c r="B55" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55">
+        <v>3000000044</v>
+      </c>
+      <c r="D55" t="s">
+        <v>258</v>
+      </c>
+      <c r="F55" t="s">
+        <v>128</v>
+      </c>
+      <c r="G55" t="s">
+        <v>253</v>
+      </c>
+      <c r="H55" t="s">
+        <v>254</v>
+      </c>
+      <c r="I55">
+        <v>1991.67</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>1</v>
+      </c>
+      <c r="L55" s="1">
+        <v>44655</v>
+      </c>
+      <c r="M55" t="s">
+        <v>182</v>
+      </c>
+      <c r="N55" t="s">
+        <v>182</v>
+      </c>
+      <c r="P55" t="s">
+        <v>182</v>
+      </c>
+      <c r="R55" t="s">
+        <v>129</v>
+      </c>
+      <c r="S55" t="s">
+        <v>130</v>
+      </c>
+      <c r="T55" t="s">
+        <v>131</v>
+      </c>
+      <c r="U55" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21">
+      <c r="A56" t="s">
+        <v>51</v>
+      </c>
+      <c r="B56" t="s">
+        <v>126</v>
+      </c>
+      <c r="C56">
+        <v>3000000044</v>
+      </c>
+      <c r="D56" t="s">
+        <v>259</v>
+      </c>
+      <c r="F56" t="s">
+        <v>128</v>
+      </c>
+      <c r="G56" t="s">
+        <v>256</v>
+      </c>
+      <c r="H56" t="s">
+        <v>257</v>
+      </c>
+      <c r="I56">
+        <v>-7</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
+      </c>
+      <c r="L56" s="1">
+        <v>44655</v>
+      </c>
+      <c r="M56" t="s">
+        <v>182</v>
+      </c>
+      <c r="N56" t="s">
+        <v>182</v>
+      </c>
+      <c r="P56" t="s">
+        <v>182</v>
+      </c>
+      <c r="R56" t="s">
+        <v>129</v>
+      </c>
+      <c r="S56" t="s">
+        <v>130</v>
+      </c>
+      <c r="T56" t="s">
+        <v>131</v>
+      </c>
+      <c r="U56" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21">
+      <c r="A57" t="s">
+        <v>51</v>
+      </c>
+      <c r="D57" t="s">
+        <v>133</v>
+      </c>
+      <c r="F57" t="s">
+        <v>54</v>
+      </c>
+      <c r="G57" t="s">
+        <v>54</v>
+      </c>
+      <c r="H57" t="s">
+        <v>192</v>
+      </c>
+      <c r="I57">
+        <v>-8.23</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>1</v>
+      </c>
+      <c r="L57" s="1">
+        <v>44652</v>
+      </c>
+      <c r="M57" t="s">
+        <v>182</v>
+      </c>
+      <c r="N57" t="s">
+        <v>182</v>
+      </c>
+      <c r="P57" t="s">
+        <v>182</v>
+      </c>
+      <c r="U57" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21">
+      <c r="A58" t="s">
+        <v>32</v>
+      </c>
+      <c r="C58">
+        <v>3000000033</v>
+      </c>
+      <c r="D58" t="s">
+        <v>260</v>
+      </c>
+      <c r="E58" t="s">
+        <v>134</v>
+      </c>
+      <c r="F58" t="s">
+        <v>35</v>
+      </c>
+      <c r="G58" t="s">
+        <v>179</v>
+      </c>
+      <c r="H58" t="s">
+        <v>180</v>
+      </c>
+      <c r="I58">
+        <v>16.49</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0.748089</v>
+      </c>
+      <c r="L58" s="1">
+        <v>44651</v>
+      </c>
+      <c r="M58" t="s">
+        <v>261</v>
+      </c>
+      <c r="N58" t="s">
+        <v>182</v>
+      </c>
+      <c r="O58">
+        <v>300</v>
+      </c>
+      <c r="P58" t="s">
+        <v>183</v>
+      </c>
+      <c r="R58" t="s">
+        <v>38</v>
+      </c>
+      <c r="S58" t="s">
+        <v>39</v>
+      </c>
+      <c r="T58" t="s">
+        <v>40</v>
+      </c>
+      <c r="U58" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21">
+      <c r="A59" t="s">
+        <v>32</v>
+      </c>
+      <c r="C59">
+        <v>3000000033</v>
+      </c>
+      <c r="D59" t="s">
+        <v>262</v>
+      </c>
+      <c r="E59" t="s">
+        <v>134</v>
+      </c>
+      <c r="F59" t="s">
+        <v>35</v>
+      </c>
+      <c r="G59" t="s">
+        <v>185</v>
+      </c>
+      <c r="H59" t="s">
+        <v>186</v>
+      </c>
+      <c r="I59">
+        <v>-4.13</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0.748089</v>
+      </c>
+      <c r="L59" s="1">
+        <v>44651</v>
+      </c>
+      <c r="M59" t="s">
+        <v>261</v>
+      </c>
+      <c r="N59" t="s">
+        <v>182</v>
+      </c>
+      <c r="O59">
+        <v>300</v>
+      </c>
+      <c r="P59" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q59">
+        <v>25</v>
+      </c>
+      <c r="R59" t="s">
+        <v>38</v>
+      </c>
+      <c r="S59" t="s">
+        <v>39</v>
+      </c>
+      <c r="T59" t="s">
+        <v>40</v>
+      </c>
+      <c r="U59" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21">
+      <c r="A60" t="s">
+        <v>44</v>
+      </c>
+      <c r="C60">
+        <v>3000000022</v>
+      </c>
+      <c r="D60" t="s">
+        <v>263</v>
+      </c>
+      <c r="E60" t="s">
+        <v>135</v>
+      </c>
+      <c r="F60" t="s">
+        <v>35</v>
+      </c>
+      <c r="G60" t="s">
+        <v>185</v>
+      </c>
+      <c r="H60" t="s">
+        <v>186</v>
+      </c>
+      <c r="I60">
+        <v>-0.52</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0.841859</v>
+      </c>
+      <c r="L60" s="1">
+        <v>44630</v>
+      </c>
+      <c r="M60" t="s">
+        <v>264</v>
+      </c>
+      <c r="N60" t="s">
+        <v>182</v>
+      </c>
+      <c r="O60">
+        <v>3</v>
+      </c>
+      <c r="P60" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q60">
+        <v>30</v>
+      </c>
+      <c r="R60" t="s">
+        <v>47</v>
+      </c>
+      <c r="S60" t="s">
+        <v>48</v>
+      </c>
+      <c r="T60" t="s">
+        <v>49</v>
+      </c>
+      <c r="U60" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21">
+      <c r="A61" t="s">
+        <v>44</v>
+      </c>
+      <c r="C61">
+        <v>3000000022</v>
+      </c>
+      <c r="D61" t="s">
+        <v>265</v>
+      </c>
+      <c r="E61" t="s">
+        <v>135</v>
+      </c>
+      <c r="F61" t="s">
+        <v>35</v>
+      </c>
+      <c r="G61" t="s">
+        <v>179</v>
+      </c>
+      <c r="H61" t="s">
+        <v>180</v>
+      </c>
+      <c r="I61">
+        <v>1.73</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0.841859</v>
+      </c>
+      <c r="L61" s="1">
+        <v>44630</v>
+      </c>
+      <c r="M61" t="s">
+        <v>264</v>
+      </c>
+      <c r="N61" t="s">
+        <v>182</v>
+      </c>
+      <c r="O61">
+        <v>3</v>
+      </c>
+      <c r="P61" t="s">
+        <v>206</v>
+      </c>
+      <c r="R61" t="s">
+        <v>47</v>
+      </c>
+      <c r="S61" t="s">
+        <v>48</v>
+      </c>
+      <c r="T61" t="s">
+        <v>49</v>
+      </c>
+      <c r="U61" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21">
+      <c r="A62" t="s">
+        <v>51</v>
+      </c>
+      <c r="D62" t="s">
+        <v>136</v>
+      </c>
+      <c r="F62" t="s">
+        <v>54</v>
+      </c>
+      <c r="G62" t="s">
+        <v>54</v>
+      </c>
+      <c r="H62" t="s">
+        <v>192</v>
+      </c>
+      <c r="I62">
+        <v>-8.56</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>1</v>
+      </c>
+      <c r="L62" s="1">
+        <v>44623</v>
+      </c>
+      <c r="M62" t="s">
+        <v>182</v>
+      </c>
+      <c r="N62" t="s">
+        <v>182</v>
+      </c>
+      <c r="P62" t="s">
+        <v>182</v>
+      </c>
+      <c r="U62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21">
+      <c r="A63" t="s">
+        <v>32</v>
+      </c>
+      <c r="C63">
+        <v>3000000011</v>
+      </c>
+      <c r="D63" t="s">
+        <v>266</v>
+      </c>
+      <c r="E63" t="s">
+        <v>137</v>
+      </c>
+      <c r="F63" t="s">
+        <v>35</v>
+      </c>
+      <c r="G63" t="s">
+        <v>185</v>
+      </c>
+      <c r="H63" t="s">
+        <v>186</v>
+      </c>
+      <c r="I63">
+        <v>-4.23</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0.692874</v>
+      </c>
+      <c r="L63" s="1">
+        <v>44620</v>
+      </c>
+      <c r="M63" t="s">
+        <v>267</v>
+      </c>
+      <c r="N63" t="s">
+        <v>182</v>
+      </c>
+      <c r="O63">
+        <v>300</v>
+      </c>
+      <c r="P63" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q63">
+        <v>25</v>
+      </c>
+      <c r="R63" t="s">
+        <v>38</v>
+      </c>
+      <c r="S63" t="s">
+        <v>39</v>
+      </c>
+      <c r="T63" t="s">
+        <v>40</v>
+      </c>
+      <c r="U63" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21">
+      <c r="A64" t="s">
+        <v>32</v>
+      </c>
+      <c r="C64">
+        <v>3000000011</v>
+      </c>
+      <c r="D64" t="s">
+        <v>268</v>
+      </c>
+      <c r="E64" t="s">
+        <v>137</v>
+      </c>
+      <c r="F64" t="s">
+        <v>35</v>
+      </c>
+      <c r="G64" t="s">
+        <v>179</v>
+      </c>
+      <c r="H64" t="s">
+        <v>180</v>
+      </c>
+      <c r="I64">
+        <v>16.82</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0.692874</v>
+      </c>
+      <c r="L64" s="1">
+        <v>44620</v>
+      </c>
+      <c r="M64" t="s">
+        <v>267</v>
+      </c>
+      <c r="N64" t="s">
+        <v>182</v>
+      </c>
+      <c r="O64">
+        <v>300</v>
+      </c>
+      <c r="P64" t="s">
+        <v>183</v>
+      </c>
+      <c r="R64" t="s">
+        <v>38</v>
+      </c>
+      <c r="S64" t="s">
+        <v>39</v>
+      </c>
+      <c r="T64" t="s">
+        <v>40</v>
+      </c>
+      <c r="U64" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21">
+      <c r="A65" t="s">
+        <v>51</v>
+      </c>
+      <c r="D65" t="s">
+        <v>138</v>
+      </c>
+      <c r="F65" t="s">
+        <v>54</v>
+      </c>
+      <c r="G65" t="s">
+        <v>54</v>
+      </c>
+      <c r="H65" t="s">
+        <v>192</v>
+      </c>
+      <c r="I65">
+        <v>-9.35</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>1</v>
+      </c>
+      <c r="L65" s="1">
+        <v>44595</v>
+      </c>
+      <c r="M65" t="s">
+        <v>182</v>
+      </c>
+      <c r="N65" t="s">
+        <v>182</v>
+      </c>
+      <c r="P65" t="s">
+        <v>182</v>
+      </c>
+      <c r="U65" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21">
+      <c r="A66" t="s">
+        <v>32</v>
+      </c>
+      <c r="C66">
+        <v>3000000000</v>
+      </c>
+      <c r="D66" t="s">
+        <v>269</v>
+      </c>
+      <c r="E66" t="s">
+        <v>139</v>
+      </c>
+      <c r="F66" t="s">
+        <v>35</v>
+      </c>
+      <c r="G66" t="s">
+        <v>179</v>
+      </c>
+      <c r="H66" t="s">
+        <v>180</v>
+      </c>
+      <c r="I66">
+        <v>15.86</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0.659724</v>
+      </c>
+      <c r="L66" s="1">
+        <v>44592</v>
+      </c>
+      <c r="M66" t="s">
+        <v>270</v>
+      </c>
+      <c r="N66" t="s">
+        <v>182</v>
+      </c>
+      <c r="O66">
+        <v>300</v>
+      </c>
+      <c r="P66" t="s">
+        <v>183</v>
+      </c>
+      <c r="R66" t="s">
+        <v>38</v>
+      </c>
+      <c r="S66" t="s">
+        <v>39</v>
+      </c>
+      <c r="T66" t="s">
+        <v>40</v>
+      </c>
+      <c r="U66" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21">
+      <c r="A67" t="s">
+        <v>32</v>
+      </c>
+      <c r="C67">
+        <v>3000000000</v>
+      </c>
+      <c r="D67" t="s">
+        <v>271</v>
+      </c>
+      <c r="E67" t="s">
+        <v>139</v>
+      </c>
+      <c r="F67" t="s">
+        <v>35</v>
+      </c>
+      <c r="G67" t="s">
+        <v>185</v>
+      </c>
+      <c r="H67" t="s">
+        <v>186</v>
+      </c>
+      <c r="I67">
+        <v>-3.97</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0.659724</v>
+      </c>
+      <c r="L67" s="1">
+        <v>44592</v>
+      </c>
+      <c r="M67" t="s">
+        <v>270</v>
+      </c>
+      <c r="N67" t="s">
+        <v>182</v>
+      </c>
+      <c r="O67">
+        <v>300</v>
+      </c>
+      <c r="P67" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q67">
+        <v>25</v>
+      </c>
+      <c r="R67" t="s">
+        <v>38</v>
+      </c>
+      <c r="S67" t="s">
+        <v>39</v>
+      </c>
+      <c r="T67" t="s">
+        <v>40</v>
+      </c>
+      <c r="U67" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21">
+      <c r="A68" t="s">
+        <v>51</v>
+      </c>
+      <c r="D68" t="s">
+        <v>272</v>
+      </c>
+      <c r="E68" t="s">
+        <v>140</v>
+      </c>
+      <c r="F68" t="s">
+        <v>67</v>
+      </c>
+      <c r="G68" t="s">
+        <v>273</v>
+      </c>
+      <c r="H68" t="s">
+        <v>274</v>
+      </c>
+      <c r="I68">
+        <v>240</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>1</v>
+      </c>
+      <c r="L68" s="1">
+        <v>44578</v>
+      </c>
+      <c r="M68" t="s">
+        <v>270</v>
+      </c>
+      <c r="N68" t="s">
+        <v>275</v>
+      </c>
+      <c r="O68">
+        <v>3000</v>
+      </c>
+      <c r="P68" t="s">
+        <v>182</v>
+      </c>
+      <c r="R68" t="s">
+        <v>141</v>
+      </c>
+      <c r="S68" t="s">
+        <v>142</v>
+      </c>
+      <c r="T68" t="s">
+        <v>143</v>
+      </c>
+      <c r="U68" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21">
+      <c r="A69" t="s">
+        <v>51</v>
+      </c>
+      <c r="D69" t="s">
+        <v>146</v>
+      </c>
+      <c r="F69" t="s">
+        <v>54</v>
+      </c>
+      <c r="G69" t="s">
+        <v>54</v>
+      </c>
+      <c r="H69" t="s">
+        <v>192</v>
+      </c>
+      <c r="I69">
+        <v>-8.66</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>1</v>
+      </c>
+      <c r="L69" s="1">
+        <v>44566</v>
+      </c>
+      <c r="M69" t="s">
+        <v>182</v>
+      </c>
+      <c r="N69" t="s">
+        <v>182</v>
+      </c>
+      <c r="P69" t="s">
+        <v>182</v>
+      </c>
+      <c r="U69" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>